--- a/data/nzd0220/nzd0220.xlsx
+++ b/data/nzd0220/nzd0220.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R427"/>
+  <dimension ref="A1:R430"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26078,6 +26078,186 @@
         <v>379.29</v>
       </c>
       <c r="R427" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-27 21:59:12+00:00</t>
+        </is>
+      </c>
+      <c r="B428" t="n">
+        <v>382.83</v>
+      </c>
+      <c r="C428" t="n">
+        <v>377.89</v>
+      </c>
+      <c r="D428" t="n">
+        <v>379.92</v>
+      </c>
+      <c r="E428" t="n">
+        <v>384.15</v>
+      </c>
+      <c r="F428" t="n">
+        <v>383.56</v>
+      </c>
+      <c r="G428" t="n">
+        <v>384.76</v>
+      </c>
+      <c r="H428" t="n">
+        <v>391.22</v>
+      </c>
+      <c r="I428" t="n">
+        <v>383.94</v>
+      </c>
+      <c r="J428" t="n">
+        <v>376.25</v>
+      </c>
+      <c r="K428" t="n">
+        <v>368.96</v>
+      </c>
+      <c r="L428" t="n">
+        <v>369.81</v>
+      </c>
+      <c r="M428" t="n">
+        <v>372.21</v>
+      </c>
+      <c r="N428" t="n">
+        <v>375.53</v>
+      </c>
+      <c r="O428" t="n">
+        <v>372.08</v>
+      </c>
+      <c r="P428" t="n">
+        <v>368.01</v>
+      </c>
+      <c r="Q428" t="n">
+        <v>378.47</v>
+      </c>
+      <c r="R428" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-05 21:59:22+00:00</t>
+        </is>
+      </c>
+      <c r="B429" t="n">
+        <v>381.49</v>
+      </c>
+      <c r="C429" t="n">
+        <v>377.05</v>
+      </c>
+      <c r="D429" t="n">
+        <v>378.89</v>
+      </c>
+      <c r="E429" t="n">
+        <v>382.56</v>
+      </c>
+      <c r="F429" t="n">
+        <v>382.31</v>
+      </c>
+      <c r="G429" t="n">
+        <v>384.07</v>
+      </c>
+      <c r="H429" t="n">
+        <v>390.98</v>
+      </c>
+      <c r="I429" t="n">
+        <v>383.85</v>
+      </c>
+      <c r="J429" t="n">
+        <v>375.54</v>
+      </c>
+      <c r="K429" t="n">
+        <v>368.72</v>
+      </c>
+      <c r="L429" t="n">
+        <v>369.85</v>
+      </c>
+      <c r="M429" t="n">
+        <v>372.05</v>
+      </c>
+      <c r="N429" t="n">
+        <v>375.1</v>
+      </c>
+      <c r="O429" t="n">
+        <v>371.09</v>
+      </c>
+      <c r="P429" t="n">
+        <v>367.72</v>
+      </c>
+      <c r="Q429" t="n">
+        <v>378.12</v>
+      </c>
+      <c r="R429" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-21 21:59:33+00:00</t>
+        </is>
+      </c>
+      <c r="B430" t="n">
+        <v>381.68</v>
+      </c>
+      <c r="C430" t="n">
+        <v>377.85</v>
+      </c>
+      <c r="D430" t="n">
+        <v>379.98</v>
+      </c>
+      <c r="E430" t="n">
+        <v>383.18</v>
+      </c>
+      <c r="F430" t="n">
+        <v>382.35</v>
+      </c>
+      <c r="G430" t="n">
+        <v>384.59</v>
+      </c>
+      <c r="H430" t="n">
+        <v>391.44</v>
+      </c>
+      <c r="I430" t="n">
+        <v>383.58</v>
+      </c>
+      <c r="J430" t="n">
+        <v>375.77</v>
+      </c>
+      <c r="K430" t="n">
+        <v>368.72</v>
+      </c>
+      <c r="L430" t="n">
+        <v>370.65</v>
+      </c>
+      <c r="M430" t="n">
+        <v>373.04</v>
+      </c>
+      <c r="N430" t="n">
+        <v>376.58</v>
+      </c>
+      <c r="O430" t="n">
+        <v>371.52</v>
+      </c>
+      <c r="P430" t="n">
+        <v>368.4</v>
+      </c>
+      <c r="Q430" t="n">
+        <v>378.99</v>
+      </c>
+      <c r="R430" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -26094,7 +26274,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B431"/>
+  <dimension ref="A1:B434"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30407,6 +30587,36 @@
       </c>
       <c r="B431" t="n">
         <v>0.6899999999999999</v>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" t="inlineStr">
+        <is>
+          <t>2026-06-27 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B432" t="n">
+        <v>-0.55</v>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" t="inlineStr">
+        <is>
+          <t>2026-07-05 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B433" t="n">
+        <v>0.48</v>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" t="inlineStr">
+        <is>
+          <t>2026-07-21 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B434" t="n">
+        <v>0.02</v>
       </c>
     </row>
   </sheetData>
@@ -30575,28 +30785,28 @@
         <v>0.0468</v>
       </c>
       <c r="I2" t="n">
-        <v>0.5518893218041278</v>
+        <v>0.5513297895959164</v>
       </c>
       <c r="J2" t="n">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="K2" t="n">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="L2" t="n">
-        <v>0.4566139401132655</v>
+        <v>0.4596905747441394</v>
       </c>
       <c r="M2" t="n">
-        <v>3.601554483877778</v>
+        <v>3.580957970162762</v>
       </c>
       <c r="N2" t="n">
-        <v>20.78272037156258</v>
+        <v>20.64112975736141</v>
       </c>
       <c r="O2" t="n">
-        <v>4.558806902201779</v>
+        <v>4.543251011925427</v>
       </c>
       <c r="P2" t="n">
-        <v>367.6463590158723</v>
+        <v>367.652279927099</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -30657,28 +30867,28 @@
         <v>0.0542</v>
       </c>
       <c r="I3" t="n">
-        <v>0.8724105479021985</v>
+        <v>0.8630217375833692</v>
       </c>
       <c r="J3" t="n">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="K3" t="n">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="L3" t="n">
-        <v>0.6217196691131082</v>
+        <v>0.6169761239344973</v>
       </c>
       <c r="M3" t="n">
-        <v>4.11183407270215</v>
+        <v>4.135150088999921</v>
       </c>
       <c r="N3" t="n">
-        <v>26.55217206545856</v>
+        <v>26.71373172904422</v>
       </c>
       <c r="O3" t="n">
-        <v>5.1528799777851</v>
+        <v>5.16853284105308</v>
       </c>
       <c r="P3" t="n">
-        <v>361.3545242585092</v>
+        <v>361.4537559890134</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -30735,28 +30945,28 @@
         <v>0.07049999999999999</v>
       </c>
       <c r="I4" t="n">
-        <v>0.9927209394000361</v>
+        <v>0.9840519579635751</v>
       </c>
       <c r="J4" t="n">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="K4" t="n">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="L4" t="n">
-        <v>0.6958654337877256</v>
+        <v>0.692687633743629</v>
       </c>
       <c r="M4" t="n">
-        <v>3.814495820471811</v>
+        <v>3.836024676784491</v>
       </c>
       <c r="N4" t="n">
-        <v>24.69641807747658</v>
+        <v>24.82059930240438</v>
       </c>
       <c r="O4" t="n">
-        <v>4.969549081906383</v>
+        <v>4.982027629630769</v>
       </c>
       <c r="P4" t="n">
-        <v>359.5870742310331</v>
+        <v>359.6786969031797</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -30813,28 +31023,28 @@
         <v>0.0895</v>
       </c>
       <c r="I5" t="n">
-        <v>0.9519545314512978</v>
+        <v>0.9446724822144005</v>
       </c>
       <c r="J5" t="n">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="K5" t="n">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="L5" t="n">
-        <v>0.7055806306528913</v>
+        <v>0.7033902064378867</v>
       </c>
       <c r="M5" t="n">
-        <v>3.731771264886937</v>
+        <v>3.746452720878779</v>
       </c>
       <c r="N5" t="n">
-        <v>21.68159481467753</v>
+        <v>21.7412895850283</v>
       </c>
       <c r="O5" t="n">
-        <v>4.656349945469898</v>
+        <v>4.662755578520956</v>
       </c>
       <c r="P5" t="n">
-        <v>363.3240332809472</v>
+        <v>363.4010043242348</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -30891,28 +31101,28 @@
         <v>0.0858</v>
       </c>
       <c r="I6" t="n">
-        <v>0.7918370720593778</v>
+        <v>0.7879513233859347</v>
       </c>
       <c r="J6" t="n">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="K6" t="n">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="L6" t="n">
-        <v>0.565699681897078</v>
+        <v>0.5663173672306048</v>
       </c>
       <c r="M6" t="n">
-        <v>4.289703301607117</v>
+        <v>4.281155184608523</v>
       </c>
       <c r="N6" t="n">
-        <v>27.60037350645535</v>
+        <v>27.46910634356626</v>
       </c>
       <c r="O6" t="n">
-        <v>5.253605762374576</v>
+        <v>5.241097818545868</v>
       </c>
       <c r="P6" t="n">
-        <v>364.4805858130953</v>
+        <v>364.5216629788695</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -30969,28 +31179,28 @@
         <v>0.0654</v>
       </c>
       <c r="I7" t="n">
-        <v>0.6976040125112332</v>
+        <v>0.6943435410181168</v>
       </c>
       <c r="J7" t="n">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="K7" t="n">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="L7" t="n">
-        <v>0.506258376583389</v>
+        <v>0.5071750324524608</v>
       </c>
       <c r="M7" t="n">
-        <v>4.334871654676885</v>
+        <v>4.324062774441524</v>
       </c>
       <c r="N7" t="n">
-        <v>27.21350892155056</v>
+        <v>27.06557374702696</v>
       </c>
       <c r="O7" t="n">
-        <v>5.216656872130901</v>
+        <v>5.20245843299367</v>
       </c>
       <c r="P7" t="n">
-        <v>368.2658541499734</v>
+        <v>368.3003154008648</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -31047,28 +31257,28 @@
         <v>0.058</v>
       </c>
       <c r="I8" t="n">
-        <v>0.4763041085324118</v>
+        <v>0.4749890887079339</v>
       </c>
       <c r="J8" t="n">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="K8" t="n">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="L8" t="n">
-        <v>0.3983863646064584</v>
+        <v>0.4004767473467163</v>
       </c>
       <c r="M8" t="n">
-        <v>3.619253574301966</v>
+        <v>3.600929301711012</v>
       </c>
       <c r="N8" t="n">
-        <v>19.64359383484907</v>
+        <v>19.51324939701628</v>
       </c>
       <c r="O8" t="n">
-        <v>4.432109411425792</v>
+        <v>4.417380377216375</v>
       </c>
       <c r="P8" t="n">
-        <v>379.4560591108497</v>
+        <v>379.469955960964</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -31125,28 +31335,28 @@
         <v>0.0577</v>
       </c>
       <c r="I9" t="n">
-        <v>0.5891711686200231</v>
+        <v>0.5814008232846692</v>
       </c>
       <c r="J9" t="n">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="K9" t="n">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="L9" t="n">
-        <v>0.4608010297208799</v>
+        <v>0.4553006336296335</v>
       </c>
       <c r="M9" t="n">
-        <v>3.995673542512429</v>
+        <v>4.003262601057606</v>
       </c>
       <c r="N9" t="n">
-        <v>23.28936626350741</v>
+        <v>23.36380118260551</v>
       </c>
       <c r="O9" t="n">
-        <v>4.825905745402349</v>
+        <v>4.833611608580639</v>
       </c>
       <c r="P9" t="n">
-        <v>373.9008185019379</v>
+        <v>373.9829478934272</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -31203,28 +31413,28 @@
         <v>0.0703</v>
       </c>
       <c r="I10" t="n">
-        <v>0.7886344979270037</v>
+        <v>0.7787198805974647</v>
       </c>
       <c r="J10" t="n">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="K10" t="n">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="L10" t="n">
-        <v>0.5211467199322106</v>
+        <v>0.5155259799463843</v>
       </c>
       <c r="M10" t="n">
-        <v>4.775087276219663</v>
+        <v>4.789645428953901</v>
       </c>
       <c r="N10" t="n">
-        <v>32.76672866237666</v>
+        <v>32.92426304732648</v>
       </c>
       <c r="O10" t="n">
-        <v>5.724222974550927</v>
+        <v>5.737966804306772</v>
       </c>
       <c r="P10" t="n">
-        <v>362.2503502217791</v>
+        <v>362.3551429614697</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -31281,28 +31491,28 @@
         <v>0.07149999999999999</v>
       </c>
       <c r="I11" t="n">
-        <v>0.742755880397191</v>
+        <v>0.7318417543818743</v>
       </c>
       <c r="J11" t="n">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="K11" t="n">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="L11" t="n">
-        <v>0.4600223049627842</v>
+        <v>0.453171020756216</v>
       </c>
       <c r="M11" t="n">
-        <v>5.138731163604553</v>
+        <v>5.153810332874205</v>
       </c>
       <c r="N11" t="n">
-        <v>37.13027910068863</v>
+        <v>37.33854253499682</v>
       </c>
       <c r="O11" t="n">
-        <v>6.093461996327591</v>
+        <v>6.11052718961276</v>
       </c>
       <c r="P11" t="n">
-        <v>357.1799872908199</v>
+        <v>357.2953428936807</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -31359,28 +31569,28 @@
         <v>0.0635</v>
       </c>
       <c r="I12" t="n">
-        <v>0.7289727779108061</v>
+        <v>0.7210861223454191</v>
       </c>
       <c r="J12" t="n">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="K12" t="n">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="L12" t="n">
-        <v>0.3764619911503668</v>
+        <v>0.3736410330034665</v>
       </c>
       <c r="M12" t="n">
-        <v>6.040167499325666</v>
+        <v>6.033533074057472</v>
       </c>
       <c r="N12" t="n">
-        <v>50.46653686775079</v>
+        <v>50.3589436579124</v>
       </c>
       <c r="O12" t="n">
-        <v>7.103980353840429</v>
+        <v>7.096403572085821</v>
       </c>
       <c r="P12" t="n">
-        <v>356.561974128747</v>
+        <v>356.6453236597532</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -31437,28 +31647,28 @@
         <v>0.0636</v>
       </c>
       <c r="I13" t="n">
-        <v>0.7362310125645577</v>
+        <v>0.7286861578418482</v>
       </c>
       <c r="J13" t="n">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="K13" t="n">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="L13" t="n">
-        <v>0.3983131081281762</v>
+        <v>0.3957253129806588</v>
       </c>
       <c r="M13" t="n">
-        <v>5.88228759985637</v>
+        <v>5.874539615341718</v>
       </c>
       <c r="N13" t="n">
-        <v>46.94758440220786</v>
+        <v>46.84413371599951</v>
       </c>
       <c r="O13" t="n">
-        <v>6.851830733622063</v>
+        <v>6.844277442944544</v>
       </c>
       <c r="P13" t="n">
-        <v>358.4381699395232</v>
+        <v>358.517906719002</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -31515,28 +31725,28 @@
         <v>0.0607</v>
       </c>
       <c r="I14" t="n">
-        <v>0.7498838901334876</v>
+        <v>0.7411840720017536</v>
       </c>
       <c r="J14" t="n">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="K14" t="n">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="L14" t="n">
-        <v>0.3464679280961096</v>
+        <v>0.3433748606049883</v>
       </c>
       <c r="M14" t="n">
-        <v>6.776243687765398</v>
+        <v>6.772499801004199</v>
       </c>
       <c r="N14" t="n">
-        <v>60.81784100051203</v>
+        <v>60.69246368861246</v>
       </c>
       <c r="O14" t="n">
-        <v>7.798579421953208</v>
+        <v>7.790536803623513</v>
       </c>
       <c r="P14" t="n">
-        <v>362.2507461156546</v>
+        <v>362.3426878585454</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -31593,28 +31803,28 @@
         <v>0.0574</v>
       </c>
       <c r="I15" t="n">
-        <v>0.5476146711602682</v>
+        <v>0.5345681857480828</v>
       </c>
       <c r="J15" t="n">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="K15" t="n">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="L15" t="n">
-        <v>0.2492548408785359</v>
+        <v>0.240644609822143</v>
       </c>
       <c r="M15" t="n">
-        <v>6.221140229239681</v>
+        <v>6.248405349166754</v>
       </c>
       <c r="N15" t="n">
-        <v>51.78907731375693</v>
+        <v>52.09652561681884</v>
       </c>
       <c r="O15" t="n">
-        <v>7.196462833486805</v>
+        <v>7.217792295211801</v>
       </c>
       <c r="P15" t="n">
-        <v>366.7831666837303</v>
+        <v>366.9210608645055</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -31671,28 +31881,28 @@
         <v>0.0795</v>
       </c>
       <c r="I16" t="n">
-        <v>0.2754352516806488</v>
+        <v>0.2677327025615516</v>
       </c>
       <c r="J16" t="n">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="K16" t="n">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="L16" t="n">
-        <v>0.08714796070999775</v>
+        <v>0.08345996597222094</v>
       </c>
       <c r="M16" t="n">
-        <v>5.730495933554367</v>
+        <v>5.732689156370034</v>
       </c>
       <c r="N16" t="n">
-        <v>45.56394216479439</v>
+        <v>45.47887170789676</v>
       </c>
       <c r="O16" t="n">
-        <v>6.750106826176486</v>
+        <v>6.743802466553773</v>
       </c>
       <c r="P16" t="n">
-        <v>366.5031995591358</v>
+        <v>366.5846060839132</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -31749,28 +31959,28 @@
         <v>0.0578</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.09552561599401382</v>
+        <v>-0.08947188592210435</v>
       </c>
       <c r="J17" t="n">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="K17" t="n">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="L17" t="n">
-        <v>0.007093238888713604</v>
+        <v>0.006306673559029252</v>
       </c>
       <c r="M17" t="n">
-        <v>7.032101703933969</v>
+        <v>7.011751610031131</v>
       </c>
       <c r="N17" t="n">
-        <v>73.23904294728898</v>
+        <v>72.87168406711162</v>
       </c>
       <c r="O17" t="n">
-        <v>8.557981242517945</v>
+        <v>8.536491320625332</v>
       </c>
       <c r="P17" t="n">
-        <v>376.4991701166435</v>
+        <v>376.4351823163422</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -31808,7 +32018,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R427"/>
+  <dimension ref="A1:R430"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -71095,6 +71305,282 @@
         </is>
       </c>
     </row>
+    <row r="428">
+      <c r="A428" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-27 21:59:12+00:00</t>
+        </is>
+      </c>
+      <c r="B428" t="inlineStr">
+        <is>
+          <t>-37.74427154471095,176.4705093000194</t>
+        </is>
+      </c>
+      <c r="C428" t="inlineStr">
+        <is>
+          <t>-37.744941615719746,176.47081685394306</t>
+        </is>
+      </c>
+      <c r="D428" t="inlineStr">
+        <is>
+          <t>-37.745581142442845,176.47119335561592</t>
+        </is>
+      </c>
+      <c r="E428" t="inlineStr">
+        <is>
+          <t>-37.74618224842334,176.47161994158327</t>
+        </is>
+      </c>
+      <c r="F428" t="inlineStr">
+        <is>
+          <t>-37.74676713959114,176.47209692546747</t>
+        </is>
+      </c>
+      <c r="G428" t="inlineStr">
+        <is>
+          <t>-37.747352394243386,176.4726010634672</t>
+        </is>
+      </c>
+      <c r="H428" t="inlineStr">
+        <is>
+          <t>-37.747904382325295,176.47316468206327</t>
+        </is>
+      </c>
+      <c r="I428" t="inlineStr">
+        <is>
+          <t>-37.74852889813833,176.4736021174355</t>
+        </is>
+      </c>
+      <c r="J428" t="inlineStr">
+        <is>
+          <t>-37.74915047109282,176.47404123098872</t>
+        </is>
+      </c>
+      <c r="K428" t="inlineStr">
+        <is>
+          <t>-37.74976068102711,176.47450690440746</t>
+        </is>
+      </c>
+      <c r="L428" t="inlineStr">
+        <is>
+          <t>-37.75032875674909,176.47504844741954</t>
+        </is>
+      </c>
+      <c r="M428" t="inlineStr">
+        <is>
+          <t>-37.75089863413522,176.47558703301817</t>
+        </is>
+      </c>
+      <c r="N428" t="inlineStr">
+        <is>
+          <t>-37.75146352824859,176.4761315614712</t>
+        </is>
+      </c>
+      <c r="O428" t="inlineStr">
+        <is>
+          <t>-37.7520613156851,176.47661085496128</t>
+        </is>
+      </c>
+      <c r="P428" t="inlineStr">
+        <is>
+          <t>-37.752639956753704,176.47713488350612</t>
+        </is>
+      </c>
+      <c r="Q428" t="inlineStr">
+        <is>
+          <t>-37.75317870036342,176.47772928907992</t>
+        </is>
+      </c>
+      <c r="R428" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-05 21:59:22+00:00</t>
+        </is>
+      </c>
+      <c r="B429" t="inlineStr">
+        <is>
+          <t>-37.744276618625214,176.47049551681133</t>
+        </is>
+      </c>
+      <c r="C429" t="inlineStr">
+        <is>
+          <t>-37.74494479639829,176.47080821365674</t>
+        </is>
+      </c>
+      <c r="D429" t="inlineStr">
+        <is>
+          <t>-37.74558524277125,176.47118288146225</t>
+        </is>
+      </c>
+      <c r="E429" t="inlineStr">
+        <is>
+          <t>-37.74618964853877,176.471604510254</t>
+        </is>
+      </c>
+      <c r="F429" t="inlineStr">
+        <is>
+          <t>-37.746773544406004,176.472085272329</t>
+        </is>
+      </c>
+      <c r="G429" t="inlineStr">
+        <is>
+          <t>-37.74735597233554,176.47259466838517</t>
+        </is>
+      </c>
+      <c r="H429" t="inlineStr">
+        <is>
+          <t>-37.74790563976986,176.47316246919996</t>
+        </is>
+      </c>
+      <c r="I429" t="inlineStr">
+        <is>
+          <t>-37.74852937273545,176.47360129037241</t>
+        </is>
+      </c>
+      <c r="J429" t="inlineStr">
+        <is>
+          <t>-37.749154311657,176.4740347959228</t>
+        </is>
+      </c>
+      <c r="K429" t="inlineStr">
+        <is>
+          <t>-37.74976200349568,176.47450475245137</t>
+        </is>
+      </c>
+      <c r="L429" t="inlineStr">
+        <is>
+          <t>-37.75032853973181,176.47504880934943</t>
+        </is>
+      </c>
+      <c r="M429" t="inlineStr">
+        <is>
+          <t>-37.75089948732804,176.4755855713283</t>
+        </is>
+      </c>
+      <c r="N429" t="inlineStr">
+        <is>
+          <t>-37.751465818049255,176.47612763023412</t>
+        </is>
+      </c>
+      <c r="O429" t="inlineStr">
+        <is>
+          <t>-37.75206681267484,176.4766020188909</t>
+        </is>
+      </c>
+      <c r="P429" t="inlineStr">
+        <is>
+          <t>-37.75264154213666,176.47713227092774</t>
+        </is>
+      </c>
+      <c r="Q429" t="inlineStr">
+        <is>
+          <t>-37.75318050201793,176.47772603320465</t>
+        </is>
+      </c>
+      <c r="R429" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-21 21:59:33+00:00</t>
+        </is>
+      </c>
+      <c r="B430" t="inlineStr">
+        <is>
+          <t>-37.744275899189695,176.4704974711469</t>
+        </is>
+      </c>
+      <c r="C430" t="inlineStr">
+        <is>
+          <t>-37.74494176718065,176.47081644250088</t>
+        </is>
+      </c>
+      <c r="D430" t="inlineStr">
+        <is>
+          <t>-37.745580903588746,176.47119396576073</t>
+        </is>
+      </c>
+      <c r="E430" t="inlineStr">
+        <is>
+          <t>-37.74618676295939,176.47161052750226</t>
+        </is>
+      </c>
+      <c r="F430" t="inlineStr">
+        <is>
+          <t>-37.74677333945195,176.47208564522944</t>
+        </is>
+      </c>
+      <c r="G430" t="inlineStr">
+        <is>
+          <t>-37.74735327580235,176.47259948786734</t>
+        </is>
+      </c>
+      <c r="H430" t="inlineStr">
+        <is>
+          <t>-37.74790322966774,176.47316671052124</t>
+        </is>
+      </c>
+      <c r="I430" t="inlineStr">
+        <is>
+          <t>-37.748530796526715,176.47359880918304</t>
+        </is>
+      </c>
+      <c r="J430" t="inlineStr">
+        <is>
+          <t>-37.7491530675306,176.4740368805217</t>
+        </is>
+      </c>
+      <c r="K430" t="inlineStr">
+        <is>
+          <t>-37.74976200349568,176.47450475245137</t>
+        </is>
+      </c>
+      <c r="L430" t="inlineStr">
+        <is>
+          <t>-37.75032419938585,176.47505604794725</t>
+        </is>
+      </c>
+      <c r="M430" t="inlineStr">
+        <is>
+          <t>-37.750894208197245,176.47559461553365</t>
+        </is>
+      </c>
+      <c r="N430" t="inlineStr">
+        <is>
+          <t>-37.7514579368744,176.47614116100252</t>
+        </is>
+      </c>
+      <c r="O430" t="inlineStr">
+        <is>
+          <t>-37.75206442509351,176.47660585678022</t>
+        </is>
+      </c>
+      <c r="P430" t="inlineStr">
+        <is>
+          <t>-37.75263782468688,176.4771383969734</t>
+        </is>
+      </c>
+      <c r="Q430" t="inlineStr">
+        <is>
+          <t>-37.753176023619424,176.47773412638006</t>
+        </is>
+      </c>
+      <c r="R430" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0220/nzd0220.xlsx
+++ b/data/nzd0220/nzd0220.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R430"/>
+  <dimension ref="A1:R432"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26258,6 +26258,126 @@
         <v>378.99</v>
       </c>
       <c r="R430" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-29 21:59:27+00:00</t>
+        </is>
+      </c>
+      <c r="B431" t="n">
+        <v>381.77</v>
+      </c>
+      <c r="C431" t="n">
+        <v>378.32</v>
+      </c>
+      <c r="D431" t="n">
+        <v>380.87</v>
+      </c>
+      <c r="E431" t="n">
+        <v>383.88</v>
+      </c>
+      <c r="F431" t="n">
+        <v>382.32</v>
+      </c>
+      <c r="G431" t="n">
+        <v>385.04</v>
+      </c>
+      <c r="H431" t="n">
+        <v>392.06</v>
+      </c>
+      <c r="I431" t="n">
+        <v>384.37</v>
+      </c>
+      <c r="J431" t="n">
+        <v>376.5</v>
+      </c>
+      <c r="K431" t="n">
+        <v>369.26</v>
+      </c>
+      <c r="L431" t="n">
+        <v>371.12</v>
+      </c>
+      <c r="M431" t="n">
+        <v>373.24</v>
+      </c>
+      <c r="N431" t="n">
+        <v>376.9</v>
+      </c>
+      <c r="O431" t="n">
+        <v>371.67</v>
+      </c>
+      <c r="P431" t="n">
+        <v>368.72</v>
+      </c>
+      <c r="Q431" t="n">
+        <v>379.19</v>
+      </c>
+      <c r="R431" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-06 21:59:39+00:00</t>
+        </is>
+      </c>
+      <c r="B432" t="n">
+        <v>382.03</v>
+      </c>
+      <c r="C432" t="n">
+        <v>379.47</v>
+      </c>
+      <c r="D432" t="n">
+        <v>381.72</v>
+      </c>
+      <c r="E432" t="n">
+        <v>384.88</v>
+      </c>
+      <c r="F432" t="n">
+        <v>382.81</v>
+      </c>
+      <c r="G432" t="n">
+        <v>385.92</v>
+      </c>
+      <c r="H432" t="n">
+        <v>392.79</v>
+      </c>
+      <c r="I432" t="n">
+        <v>385.21</v>
+      </c>
+      <c r="J432" t="n">
+        <v>377.32</v>
+      </c>
+      <c r="K432" t="n">
+        <v>370.26</v>
+      </c>
+      <c r="L432" t="n">
+        <v>371.79</v>
+      </c>
+      <c r="M432" t="n">
+        <v>374</v>
+      </c>
+      <c r="N432" t="n">
+        <v>377.52</v>
+      </c>
+      <c r="O432" t="n">
+        <v>371.92</v>
+      </c>
+      <c r="P432" t="n">
+        <v>369.54</v>
+      </c>
+      <c r="Q432" t="n">
+        <v>379.84</v>
+      </c>
+      <c r="R432" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -26274,7 +26394,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B434"/>
+  <dimension ref="A1:B436"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30617,6 +30737,26 @@
       </c>
       <c r="B434" t="n">
         <v>0.02</v>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" t="inlineStr">
+        <is>
+          <t>2026-07-29 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B435" t="n">
+        <v>-0.07000000000000001</v>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" t="inlineStr">
+        <is>
+          <t>2026-08-06 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B436" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -30785,28 +30925,28 @@
         <v>0.0468</v>
       </c>
       <c r="I2" t="n">
-        <v>0.5513297895959164</v>
+        <v>0.5508456406742117</v>
       </c>
       <c r="J2" t="n">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="K2" t="n">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="L2" t="n">
-        <v>0.4596905747441394</v>
+        <v>0.4616282567406512</v>
       </c>
       <c r="M2" t="n">
-        <v>3.580957970162762</v>
+        <v>3.566596967490276</v>
       </c>
       <c r="N2" t="n">
-        <v>20.64112975736141</v>
+        <v>20.54682751689466</v>
       </c>
       <c r="O2" t="n">
-        <v>4.543251011925427</v>
+        <v>4.53286085346712</v>
       </c>
       <c r="P2" t="n">
-        <v>367.652279927099</v>
+        <v>367.6574126254827</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -30867,28 +31007,28 @@
         <v>0.0542</v>
       </c>
       <c r="I3" t="n">
-        <v>0.8630217375833692</v>
+        <v>0.8580224594211937</v>
       </c>
       <c r="J3" t="n">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="K3" t="n">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="L3" t="n">
-        <v>0.6169761239344973</v>
+        <v>0.6151612431146778</v>
       </c>
       <c r="M3" t="n">
-        <v>4.135150088999921</v>
+        <v>4.143602955127642</v>
       </c>
       <c r="N3" t="n">
-        <v>26.71373172904422</v>
+        <v>26.74128162117973</v>
       </c>
       <c r="O3" t="n">
-        <v>5.16853284105308</v>
+        <v>5.171197310215472</v>
       </c>
       <c r="P3" t="n">
-        <v>361.4537559890134</v>
+        <v>361.5067591562356</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -30945,28 +31085,28 @@
         <v>0.07049999999999999</v>
       </c>
       <c r="I4" t="n">
-        <v>0.9840519579635751</v>
+        <v>0.9798631237960395</v>
       </c>
       <c r="J4" t="n">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="K4" t="n">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="L4" t="n">
-        <v>0.692687633743629</v>
+        <v>0.6920082542301236</v>
       </c>
       <c r="M4" t="n">
-        <v>3.836024676784491</v>
+        <v>3.841478642705655</v>
       </c>
       <c r="N4" t="n">
-        <v>24.82059930240438</v>
+        <v>24.811538734614</v>
       </c>
       <c r="O4" t="n">
-        <v>4.982027629630769</v>
+        <v>4.98111822130473</v>
       </c>
       <c r="P4" t="n">
-        <v>359.6786969031797</v>
+        <v>359.7231078932489</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -31023,28 +31163,28 @@
         <v>0.0895</v>
       </c>
       <c r="I5" t="n">
-        <v>0.9446724822144005</v>
+        <v>0.940853337643641</v>
       </c>
       <c r="J5" t="n">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="K5" t="n">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="L5" t="n">
-        <v>0.7033902064378867</v>
+        <v>0.7028553065692429</v>
       </c>
       <c r="M5" t="n">
-        <v>3.746452720878779</v>
+        <v>3.750452652227896</v>
       </c>
       <c r="N5" t="n">
-        <v>21.7412895850283</v>
+        <v>21.72906199309289</v>
       </c>
       <c r="O5" t="n">
-        <v>4.662755578520956</v>
+        <v>4.661444196071952</v>
       </c>
       <c r="P5" t="n">
-        <v>363.4010043242348</v>
+        <v>363.441495265182</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -31101,28 +31241,28 @@
         <v>0.0858</v>
       </c>
       <c r="I6" t="n">
-        <v>0.7879513233859347</v>
+        <v>0.7852394130905032</v>
       </c>
       <c r="J6" t="n">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="K6" t="n">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="L6" t="n">
-        <v>0.5663173672306048</v>
+        <v>0.5665899474398555</v>
       </c>
       <c r="M6" t="n">
-        <v>4.281155184608523</v>
+        <v>4.276268191768357</v>
       </c>
       <c r="N6" t="n">
-        <v>27.46910634356626</v>
+        <v>27.3860478929387</v>
       </c>
       <c r="O6" t="n">
-        <v>5.241097818545868</v>
+        <v>5.233168055101871</v>
       </c>
       <c r="P6" t="n">
-        <v>364.5216629788695</v>
+        <v>364.5504154163447</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -31179,28 +31319,28 @@
         <v>0.0654</v>
       </c>
       <c r="I7" t="n">
-        <v>0.6943435410181168</v>
+        <v>0.6930709630883394</v>
       </c>
       <c r="J7" t="n">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="K7" t="n">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="L7" t="n">
-        <v>0.5071750324524608</v>
+        <v>0.5085663739549908</v>
       </c>
       <c r="M7" t="n">
-        <v>4.324062774441524</v>
+        <v>4.311542372812568</v>
       </c>
       <c r="N7" t="n">
-        <v>27.06557374702696</v>
+        <v>26.95055446147527</v>
       </c>
       <c r="O7" t="n">
-        <v>5.20245843299367</v>
+        <v>5.191392343242348</v>
       </c>
       <c r="P7" t="n">
-        <v>368.3003154008648</v>
+        <v>368.3138061600991</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -31257,28 +31397,28 @@
         <v>0.058</v>
       </c>
       <c r="I8" t="n">
-        <v>0.4749890887079339</v>
+        <v>0.4751687924137261</v>
       </c>
       <c r="J8" t="n">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="K8" t="n">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="L8" t="n">
-        <v>0.4004767473467163</v>
+        <v>0.4029628092957819</v>
       </c>
       <c r="M8" t="n">
-        <v>3.600929301711012</v>
+        <v>3.585876111457151</v>
       </c>
       <c r="N8" t="n">
-        <v>19.51324939701628</v>
+        <v>19.4234918471651</v>
       </c>
       <c r="O8" t="n">
-        <v>4.417380377216375</v>
+        <v>4.407209076860899</v>
       </c>
       <c r="P8" t="n">
-        <v>379.469955960964</v>
+        <v>379.4680489481025</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -31335,28 +31475,28 @@
         <v>0.0577</v>
       </c>
       <c r="I9" t="n">
-        <v>0.5814008232846692</v>
+        <v>0.5772111874512214</v>
       </c>
       <c r="J9" t="n">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="K9" t="n">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="L9" t="n">
-        <v>0.4553006336296335</v>
+        <v>0.4529727606232506</v>
       </c>
       <c r="M9" t="n">
-        <v>4.003262601057606</v>
+        <v>4.003676189074503</v>
       </c>
       <c r="N9" t="n">
-        <v>23.36380118260551</v>
+        <v>23.36153710865898</v>
       </c>
       <c r="O9" t="n">
-        <v>4.833611608580639</v>
+        <v>4.833377401844282</v>
       </c>
       <c r="P9" t="n">
-        <v>373.9829478934272</v>
+        <v>374.0273673879971</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -31413,28 +31553,28 @@
         <v>0.0703</v>
       </c>
       <c r="I10" t="n">
-        <v>0.7787198805974647</v>
+        <v>0.7731816707169812</v>
       </c>
       <c r="J10" t="n">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="K10" t="n">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="L10" t="n">
-        <v>0.5155259799463843</v>
+        <v>0.5129602708035764</v>
       </c>
       <c r="M10" t="n">
-        <v>4.789645428953901</v>
+        <v>4.794385298322561</v>
       </c>
       <c r="N10" t="n">
-        <v>32.92426304732648</v>
+        <v>32.9563288492432</v>
       </c>
       <c r="O10" t="n">
-        <v>5.737966804306772</v>
+        <v>5.740760302367901</v>
       </c>
       <c r="P10" t="n">
-        <v>362.3551429614697</v>
+        <v>362.4138610232537</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -31491,28 +31631,28 @@
         <v>0.07149999999999999</v>
       </c>
       <c r="I11" t="n">
-        <v>0.7318417543818743</v>
+        <v>0.7255745503415257</v>
       </c>
       <c r="J11" t="n">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="K11" t="n">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="L11" t="n">
-        <v>0.453171020756216</v>
+        <v>0.4497223104904119</v>
       </c>
       <c r="M11" t="n">
-        <v>5.153810332874205</v>
+        <v>5.158933940784003</v>
       </c>
       <c r="N11" t="n">
-        <v>37.33854253499682</v>
+        <v>37.40215477874056</v>
       </c>
       <c r="O11" t="n">
-        <v>6.11052718961276</v>
+        <v>6.115730110031063</v>
       </c>
       <c r="P11" t="n">
-        <v>357.2953428936807</v>
+        <v>357.3617898371947</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -31569,28 +31709,28 @@
         <v>0.0635</v>
       </c>
       <c r="I12" t="n">
-        <v>0.7210861223454191</v>
+        <v>0.7171145961345203</v>
       </c>
       <c r="J12" t="n">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="K12" t="n">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="L12" t="n">
-        <v>0.3736410330034665</v>
+        <v>0.3728656109144808</v>
       </c>
       <c r="M12" t="n">
-        <v>6.033533074057472</v>
+        <v>6.023657338064767</v>
       </c>
       <c r="N12" t="n">
-        <v>50.3589436579124</v>
+        <v>50.22043595307153</v>
       </c>
       <c r="O12" t="n">
-        <v>7.096403572085821</v>
+        <v>7.086637845485794</v>
       </c>
       <c r="P12" t="n">
-        <v>356.6453236597532</v>
+        <v>356.6874309961905</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -31647,28 +31787,28 @@
         <v>0.0636</v>
       </c>
       <c r="I13" t="n">
-        <v>0.7286861578418482</v>
+        <v>0.7247964256812944</v>
       </c>
       <c r="J13" t="n">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="K13" t="n">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="L13" t="n">
-        <v>0.3957253129806588</v>
+        <v>0.3949995160050718</v>
       </c>
       <c r="M13" t="n">
-        <v>5.874539615341718</v>
+        <v>5.864316532619034</v>
       </c>
       <c r="N13" t="n">
-        <v>46.84413371599951</v>
+        <v>46.71822274808413</v>
       </c>
       <c r="O13" t="n">
-        <v>6.844277442944544</v>
+        <v>6.835072987765686</v>
       </c>
       <c r="P13" t="n">
-        <v>358.517906719002</v>
+        <v>358.5591466122978</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -31725,28 +31865,28 @@
         <v>0.0607</v>
       </c>
       <c r="I14" t="n">
-        <v>0.7411840720017536</v>
+        <v>0.7367919370680689</v>
       </c>
       <c r="J14" t="n">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="K14" t="n">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="L14" t="n">
-        <v>0.3433748606049883</v>
+        <v>0.342432889468602</v>
       </c>
       <c r="M14" t="n">
-        <v>6.772499801004199</v>
+        <v>6.763248657049389</v>
       </c>
       <c r="N14" t="n">
-        <v>60.69246368861246</v>
+        <v>60.52703643946558</v>
       </c>
       <c r="O14" t="n">
-        <v>7.790536803623513</v>
+        <v>7.779912367081366</v>
       </c>
       <c r="P14" t="n">
-        <v>362.3426878585454</v>
+        <v>362.3892549077181</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -31803,28 +31943,28 @@
         <v>0.0574</v>
       </c>
       <c r="I15" t="n">
-        <v>0.5345681857480828</v>
+        <v>0.526297975188428</v>
       </c>
       <c r="J15" t="n">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="K15" t="n">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="L15" t="n">
-        <v>0.240644609822143</v>
+        <v>0.2353057610178432</v>
       </c>
       <c r="M15" t="n">
-        <v>6.248405349166754</v>
+        <v>6.263804890398386</v>
       </c>
       <c r="N15" t="n">
-        <v>52.09652561681884</v>
+        <v>52.26533338571867</v>
       </c>
       <c r="O15" t="n">
-        <v>7.217792295211801</v>
+        <v>7.229476702066248</v>
       </c>
       <c r="P15" t="n">
-        <v>366.9210608645055</v>
+        <v>367.0087468089725</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -31881,28 +32021,28 @@
         <v>0.0795</v>
       </c>
       <c r="I16" t="n">
-        <v>0.2677327025615516</v>
+        <v>0.2636824173935685</v>
       </c>
       <c r="J16" t="n">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="K16" t="n">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="L16" t="n">
-        <v>0.08345996597222094</v>
+        <v>0.08171365940037612</v>
       </c>
       <c r="M16" t="n">
-        <v>5.732689156370034</v>
+        <v>5.728282984488668</v>
       </c>
       <c r="N16" t="n">
-        <v>45.47887170789676</v>
+        <v>45.36708507490255</v>
       </c>
       <c r="O16" t="n">
-        <v>6.743802466553773</v>
+        <v>6.735509266187862</v>
       </c>
       <c r="P16" t="n">
-        <v>366.5846060839132</v>
+        <v>366.6275480968771</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -31959,28 +32099,28 @@
         <v>0.0578</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.08947188592210435</v>
+        <v>-0.08468665979332506</v>
       </c>
       <c r="J17" t="n">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="K17" t="n">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="L17" t="n">
-        <v>0.006306673559029252</v>
+        <v>0.005697442044787615</v>
       </c>
       <c r="M17" t="n">
-        <v>7.011751610031131</v>
+        <v>7.002241483643792</v>
       </c>
       <c r="N17" t="n">
-        <v>72.87168406711162</v>
+        <v>72.67143174489352</v>
       </c>
       <c r="O17" t="n">
-        <v>8.536491320625332</v>
+        <v>8.524754057736418</v>
       </c>
       <c r="P17" t="n">
-        <v>376.4351823163422</v>
+        <v>376.3844445304892</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -32018,7 +32158,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R430"/>
+  <dimension ref="A1:R432"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -71581,6 +71721,190 @@
         </is>
       </c>
     </row>
+    <row r="431">
+      <c r="A431" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-29 21:59:27+00:00</t>
+        </is>
+      </c>
+      <c r="B431" t="inlineStr">
+        <is>
+          <t>-37.744275558404446,176.4704983968848</t>
+        </is>
+      </c>
+      <c r="C431" t="inlineStr">
+        <is>
+          <t>-37.744939987515025,176.4708212769465</t>
+        </is>
+      </c>
+      <c r="D431" t="inlineStr">
+        <is>
+          <t>-37.7455773605858,176.47120301624201</t>
+        </is>
+      </c>
+      <c r="E431" t="inlineStr">
+        <is>
+          <t>-37.74618350504686,176.4716173211691</t>
+        </is>
+      </c>
+      <c r="F431" t="inlineStr">
+        <is>
+          <t>-37.746773493167495,176.4720853655541</t>
+        </is>
+      </c>
+      <c r="G431" t="inlineStr">
+        <is>
+          <t>-37.747350942263864,176.4726036585728</t>
+        </is>
+      </c>
+      <c r="H431" t="inlineStr">
+        <is>
+          <t>-37.747899981269,176.4731724270843</t>
+        </is>
+      </c>
+      <c r="I431" t="inlineStr">
+        <is>
+          <t>-37.74852663061876,176.47360606895904</t>
+        </is>
+      </c>
+      <c r="J431" t="inlineStr">
+        <is>
+          <t>-37.74914911878142,176.47404349685684</t>
+        </is>
+      </c>
+      <c r="K431" t="inlineStr">
+        <is>
+          <t>-37.749759027941344,176.47450959435247</t>
+        </is>
+      </c>
+      <c r="L431" t="inlineStr">
+        <is>
+          <t>-37.750321649432415,176.47506030062308</t>
+        </is>
+      </c>
+      <c r="M431" t="inlineStr">
+        <is>
+          <t>-37.75089314170609,176.4755964426457</t>
+        </is>
+      </c>
+      <c r="N431" t="inlineStr">
+        <is>
+          <t>-37.75145623283641,176.47614408657367</t>
+        </is>
+      </c>
+      <c r="O431" t="inlineStr">
+        <is>
+          <t>-37.752063592216274,176.47660719557877</t>
+        </is>
+      </c>
+      <c r="P431" t="inlineStr">
+        <is>
+          <t>-37.752636075298646,176.4771412798182</t>
+        </is>
+      </c>
+      <c r="Q431" t="inlineStr">
+        <is>
+          <t>-37.753174994102444,176.47773598688002</t>
+        </is>
+      </c>
+      <c r="R431" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-06 21:59:39+00:00</t>
+        </is>
+      </c>
+      <c r="B432" t="inlineStr">
+        <is>
+          <t>-37.74427457391367,176.4705010712387</t>
+        </is>
+      </c>
+      <c r="C432" t="inlineStr">
+        <is>
+          <t>-37.74493563301325,176.47083310590816</t>
+        </is>
+      </c>
+      <c r="D432" t="inlineStr">
+        <is>
+          <t>-37.74557397681832,176.4712116599592</t>
+        </is>
+      </c>
+      <c r="E432" t="inlineStr">
+        <is>
+          <t>-37.74617885088546,176.47162702640634</t>
+        </is>
+      </c>
+      <c r="F432" t="inlineStr">
+        <is>
+          <t>-37.74677098248018,176.47208993358464</t>
+        </is>
+      </c>
+      <c r="G432" t="inlineStr">
+        <is>
+          <t>-37.747346378899316,176.47261181461823</t>
+        </is>
+      </c>
+      <c r="H432" t="inlineStr">
+        <is>
+          <t>-37.74789615654113,176.47317915787562</t>
+        </is>
+      </c>
+      <c r="I432" t="inlineStr">
+        <is>
+          <t>-37.748522201045276,176.4736137882136</t>
+        </is>
+      </c>
+      <c r="J432" t="inlineStr">
+        <is>
+          <t>-37.7491446831997,176.47405092890367</t>
+        </is>
+      </c>
+      <c r="K432" t="inlineStr">
+        <is>
+          <t>-37.749753517655044,176.47451856083495</t>
+        </is>
+      </c>
+      <c r="L432" t="inlineStr">
+        <is>
+          <t>-37.750318014392164,176.47506636294764</t>
+        </is>
+      </c>
+      <c r="M432" t="inlineStr">
+        <is>
+          <t>-37.75088908903948,176.4756033856709</t>
+        </is>
+      </c>
+      <c r="N432" t="inlineStr">
+        <is>
+          <t>-37.751452931262605,176.4761497548674</t>
+        </is>
+      </c>
+      <c r="O432" t="inlineStr">
+        <is>
+          <t>-37.75206220408752,176.4766094269096</t>
+        </is>
+      </c>
+      <c r="P432" t="inlineStr">
+        <is>
+          <t>-37.752631592491,176.47714866710737</t>
+        </is>
+      </c>
+      <c r="Q432" t="inlineStr">
+        <is>
+          <t>-37.753171648172085,176.47774203350454</t>
+        </is>
+      </c>
+      <c r="R432" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0220/nzd0220.xlsx
+++ b/data/nzd0220/nzd0220.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R432"/>
+  <dimension ref="A1:R434"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26378,6 +26378,126 @@
         <v>379.84</v>
       </c>
       <c r="R432" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-07 21:59:48+00:00</t>
+        </is>
+      </c>
+      <c r="B433" t="n">
+        <v>379.88</v>
+      </c>
+      <c r="C433" t="n">
+        <v>377.67</v>
+      </c>
+      <c r="D433" t="n">
+        <v>381.31</v>
+      </c>
+      <c r="E433" t="n">
+        <v>384.05</v>
+      </c>
+      <c r="F433" t="n">
+        <v>382.52</v>
+      </c>
+      <c r="G433" t="n">
+        <v>385.16</v>
+      </c>
+      <c r="H433" t="n">
+        <v>392.09</v>
+      </c>
+      <c r="I433" t="n">
+        <v>384.51</v>
+      </c>
+      <c r="J433" t="n">
+        <v>376.45</v>
+      </c>
+      <c r="K433" t="n">
+        <v>369.6</v>
+      </c>
+      <c r="L433" t="n">
+        <v>371.25</v>
+      </c>
+      <c r="M433" t="n">
+        <v>374.01</v>
+      </c>
+      <c r="N433" t="n">
+        <v>376.14</v>
+      </c>
+      <c r="O433" t="n">
+        <v>369.85</v>
+      </c>
+      <c r="P433" t="n">
+        <v>369.18</v>
+      </c>
+      <c r="Q433" t="n">
+        <v>380.38</v>
+      </c>
+      <c r="R433" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-23 21:59:53+00:00</t>
+        </is>
+      </c>
+      <c r="B434" t="n">
+        <v>379.34</v>
+      </c>
+      <c r="C434" t="n">
+        <v>377.28</v>
+      </c>
+      <c r="D434" t="n">
+        <v>381.65</v>
+      </c>
+      <c r="E434" t="n">
+        <v>384.14</v>
+      </c>
+      <c r="F434" t="n">
+        <v>382.56</v>
+      </c>
+      <c r="G434" t="n">
+        <v>385.22</v>
+      </c>
+      <c r="H434" t="n">
+        <v>392.68</v>
+      </c>
+      <c r="I434" t="n">
+        <v>384.57</v>
+      </c>
+      <c r="J434" t="n">
+        <v>376.64</v>
+      </c>
+      <c r="K434" t="n">
+        <v>369.92</v>
+      </c>
+      <c r="L434" t="n">
+        <v>371.82</v>
+      </c>
+      <c r="M434" t="n">
+        <v>374.12</v>
+      </c>
+      <c r="N434" t="n">
+        <v>375.26</v>
+      </c>
+      <c r="O434" t="n">
+        <v>369.5</v>
+      </c>
+      <c r="P434" t="n">
+        <v>369.61</v>
+      </c>
+      <c r="Q434" t="n">
+        <v>380.38</v>
+      </c>
+      <c r="R434" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -26394,7 +26514,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B436"/>
+  <dimension ref="A1:B438"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30757,6 +30877,26 @@
       </c>
       <c r="B436" t="n">
         <v>0</v>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" t="inlineStr">
+        <is>
+          <t>2026-09-07 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B437" t="n">
+        <v>-0.75</v>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" t="inlineStr">
+        <is>
+          <t>2026-09-23 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B438" t="n">
+        <v>-0.55</v>
       </c>
     </row>
   </sheetData>
@@ -30925,28 +31065,28 @@
         <v>0.0468</v>
       </c>
       <c r="I2" t="n">
-        <v>0.5508456406742117</v>
+        <v>0.5483201094673991</v>
       </c>
       <c r="J2" t="n">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="K2" t="n">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="L2" t="n">
-        <v>0.4616282567406512</v>
+        <v>0.4612743153875573</v>
       </c>
       <c r="M2" t="n">
-        <v>3.566596967490276</v>
+        <v>3.561743588987023</v>
       </c>
       <c r="N2" t="n">
-        <v>20.54682751689466</v>
+        <v>20.49062775593976</v>
       </c>
       <c r="O2" t="n">
-        <v>4.53286085346712</v>
+        <v>4.526657459532338</v>
       </c>
       <c r="P2" t="n">
-        <v>367.6574126254827</v>
+        <v>367.6843390432545</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -31007,28 +31147,28 @@
         <v>0.0542</v>
       </c>
       <c r="I3" t="n">
-        <v>0.8580224594211937</v>
+        <v>0.8517854929217312</v>
       </c>
       <c r="J3" t="n">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="K3" t="n">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="L3" t="n">
-        <v>0.6151612431146778</v>
+        <v>0.6119150500602495</v>
       </c>
       <c r="M3" t="n">
-        <v>4.143602955127642</v>
+        <v>4.1586234816523</v>
       </c>
       <c r="N3" t="n">
-        <v>26.74128162117973</v>
+        <v>26.85187717151124</v>
       </c>
       <c r="O3" t="n">
-        <v>5.171197310215472</v>
+        <v>5.181879694812611</v>
       </c>
       <c r="P3" t="n">
-        <v>361.5067591562356</v>
+        <v>361.5732513368689</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -31085,28 +31225,28 @@
         <v>0.07049999999999999</v>
       </c>
       <c r="I4" t="n">
-        <v>0.9798631237960395</v>
+        <v>0.9758042626194315</v>
       </c>
       <c r="J4" t="n">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="K4" t="n">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="L4" t="n">
-        <v>0.6920082542301236</v>
+        <v>0.6914426179931202</v>
       </c>
       <c r="M4" t="n">
-        <v>3.841478642705655</v>
+        <v>3.846251093787746</v>
       </c>
       <c r="N4" t="n">
-        <v>24.811538734614</v>
+        <v>24.79611979994451</v>
       </c>
       <c r="O4" t="n">
-        <v>4.98111822130473</v>
+        <v>4.979570242495281</v>
       </c>
       <c r="P4" t="n">
-        <v>359.7231078932489</v>
+        <v>359.7663766757969</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -31163,28 +31303,28 @@
         <v>0.0895</v>
       </c>
       <c r="I5" t="n">
-        <v>0.940853337643641</v>
+        <v>0.9367501262840124</v>
       </c>
       <c r="J5" t="n">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="K5" t="n">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="L5" t="n">
-        <v>0.7028553065692429</v>
+        <v>0.7020705719204958</v>
       </c>
       <c r="M5" t="n">
-        <v>3.750452652227896</v>
+        <v>3.755757104526118</v>
       </c>
       <c r="N5" t="n">
-        <v>21.72906199309289</v>
+        <v>21.72994672062588</v>
       </c>
       <c r="O5" t="n">
-        <v>4.661444196071952</v>
+        <v>4.66153909354259</v>
       </c>
       <c r="P5" t="n">
-        <v>363.441495265182</v>
+        <v>363.4852380268973</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -31241,28 +31381,28 @@
         <v>0.0858</v>
       </c>
       <c r="I6" t="n">
-        <v>0.7852394130905032</v>
+        <v>0.7824693073522754</v>
       </c>
       <c r="J6" t="n">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="K6" t="n">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="L6" t="n">
-        <v>0.5665899474398555</v>
+        <v>0.5668104287554721</v>
       </c>
       <c r="M6" t="n">
-        <v>4.276268191768357</v>
+        <v>4.271582936318445</v>
       </c>
       <c r="N6" t="n">
-        <v>27.3860478929387</v>
+        <v>27.30569848028194</v>
       </c>
       <c r="O6" t="n">
-        <v>5.233168055101871</v>
+        <v>5.225485477951493</v>
       </c>
       <c r="P6" t="n">
-        <v>364.5504154163447</v>
+        <v>364.5799465567033</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -31319,28 +31459,28 @@
         <v>0.0654</v>
       </c>
       <c r="I7" t="n">
-        <v>0.6930709630883394</v>
+        <v>0.691497325446489</v>
       </c>
       <c r="J7" t="n">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="K7" t="n">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="L7" t="n">
-        <v>0.5085663739549908</v>
+        <v>0.5097049793479007</v>
       </c>
       <c r="M7" t="n">
-        <v>4.311542372812568</v>
+        <v>4.300880399938028</v>
       </c>
       <c r="N7" t="n">
-        <v>26.95055446147527</v>
+        <v>26.840964841544</v>
       </c>
       <c r="O7" t="n">
-        <v>5.191392343242348</v>
+        <v>5.180826656195322</v>
       </c>
       <c r="P7" t="n">
-        <v>368.3138061600991</v>
+        <v>368.3305820310431</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -31397,28 +31537,28 @@
         <v>0.058</v>
       </c>
       <c r="I8" t="n">
-        <v>0.4751687924137261</v>
+        <v>0.4752595398621091</v>
       </c>
       <c r="J8" t="n">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="K8" t="n">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="L8" t="n">
-        <v>0.4029628092957819</v>
+        <v>0.4053750424324901</v>
       </c>
       <c r="M8" t="n">
-        <v>3.585876111457151</v>
+        <v>3.570633785631998</v>
       </c>
       <c r="N8" t="n">
-        <v>19.4234918471651</v>
+        <v>19.33420504488011</v>
       </c>
       <c r="O8" t="n">
-        <v>4.407209076860899</v>
+        <v>4.397067778063025</v>
       </c>
       <c r="P8" t="n">
-        <v>379.4680489481025</v>
+        <v>379.4670788802354</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -31475,28 +31615,28 @@
         <v>0.0577</v>
       </c>
       <c r="I9" t="n">
-        <v>0.5772111874512214</v>
+        <v>0.5728159250546333</v>
       </c>
       <c r="J9" t="n">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="K9" t="n">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="L9" t="n">
-        <v>0.4529727606232506</v>
+        <v>0.45034408743141</v>
       </c>
       <c r="M9" t="n">
-        <v>4.003676189074503</v>
+        <v>4.004868036749052</v>
       </c>
       <c r="N9" t="n">
-        <v>23.36153710865898</v>
+        <v>23.36980631231925</v>
       </c>
       <c r="O9" t="n">
-        <v>4.833377401844282</v>
+        <v>4.834232753221472</v>
       </c>
       <c r="P9" t="n">
-        <v>374.0273673879971</v>
+        <v>374.0742236381918</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -31553,28 +31693,28 @@
         <v>0.0703</v>
       </c>
       <c r="I10" t="n">
-        <v>0.7731816707169812</v>
+        <v>0.7673397431978927</v>
       </c>
       <c r="J10" t="n">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="K10" t="n">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="L10" t="n">
-        <v>0.5129602708035764</v>
+        <v>0.5100244735311348</v>
       </c>
       <c r="M10" t="n">
-        <v>4.794385298322561</v>
+        <v>4.800242315306196</v>
       </c>
       <c r="N10" t="n">
-        <v>32.9563288492432</v>
+        <v>33.00937216891749</v>
       </c>
       <c r="O10" t="n">
-        <v>5.740760302367901</v>
+        <v>5.745378331225672</v>
       </c>
       <c r="P10" t="n">
-        <v>362.4138610232537</v>
+        <v>362.4761391485727</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -31631,28 +31771,28 @@
         <v>0.07149999999999999</v>
       </c>
       <c r="I11" t="n">
-        <v>0.7255745503415257</v>
+        <v>0.7193368032262667</v>
       </c>
       <c r="J11" t="n">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="K11" t="n">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="L11" t="n">
-        <v>0.4497223104904119</v>
+        <v>0.4462899825211175</v>
       </c>
       <c r="M11" t="n">
-        <v>5.158933940784003</v>
+        <v>5.16351431799718</v>
       </c>
       <c r="N11" t="n">
-        <v>37.40215477874056</v>
+        <v>37.4634967106125</v>
       </c>
       <c r="O11" t="n">
-        <v>6.115730110031063</v>
+        <v>6.120743150191201</v>
       </c>
       <c r="P11" t="n">
-        <v>357.3617898371947</v>
+        <v>357.4282870213787</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -31709,28 +31849,28 @@
         <v>0.0635</v>
       </c>
       <c r="I12" t="n">
-        <v>0.7171145961345203</v>
+        <v>0.7132096014900343</v>
       </c>
       <c r="J12" t="n">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="K12" t="n">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="L12" t="n">
-        <v>0.3728656109144808</v>
+        <v>0.3721402659646732</v>
       </c>
       <c r="M12" t="n">
-        <v>6.023657338064767</v>
+        <v>6.01368777271028</v>
       </c>
       <c r="N12" t="n">
-        <v>50.22043595307153</v>
+        <v>50.08052094405377</v>
       </c>
       <c r="O12" t="n">
-        <v>7.086637845485794</v>
+        <v>7.07675921195951</v>
       </c>
       <c r="P12" t="n">
-        <v>356.6874309961905</v>
+        <v>356.7290583761004</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -31787,28 +31927,28 @@
         <v>0.0636</v>
       </c>
       <c r="I13" t="n">
-        <v>0.7247964256812944</v>
+        <v>0.7212831737632667</v>
       </c>
       <c r="J13" t="n">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="K13" t="n">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="L13" t="n">
-        <v>0.3949995160050718</v>
+        <v>0.3946038583756397</v>
       </c>
       <c r="M13" t="n">
-        <v>5.864316532619034</v>
+        <v>5.852459521723351</v>
       </c>
       <c r="N13" t="n">
-        <v>46.71822274808413</v>
+        <v>46.57666949931382</v>
       </c>
       <c r="O13" t="n">
-        <v>6.835072987765686</v>
+        <v>6.82471021357785</v>
       </c>
       <c r="P13" t="n">
-        <v>358.5591466122978</v>
+        <v>358.5965998355456</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -31865,28 +32005,28 @@
         <v>0.0607</v>
       </c>
       <c r="I14" t="n">
-        <v>0.7367919370680689</v>
+        <v>0.7310866101496343</v>
       </c>
       <c r="J14" t="n">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="K14" t="n">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="L14" t="n">
-        <v>0.342432889468602</v>
+        <v>0.3403758277397801</v>
       </c>
       <c r="M14" t="n">
-        <v>6.763248657049389</v>
+        <v>6.760395390316459</v>
       </c>
       <c r="N14" t="n">
-        <v>60.52703643946558</v>
+        <v>60.44411440025495</v>
       </c>
       <c r="O14" t="n">
-        <v>7.779912367081366</v>
+        <v>7.774581300639601</v>
       </c>
       <c r="P14" t="n">
-        <v>362.3892549077181</v>
+        <v>362.4500816644584</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -31943,28 +32083,28 @@
         <v>0.0574</v>
       </c>
       <c r="I15" t="n">
-        <v>0.526297975188428</v>
+        <v>0.5162700909326505</v>
       </c>
       <c r="J15" t="n">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="K15" t="n">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="L15" t="n">
-        <v>0.2353057610178432</v>
+        <v>0.2281182891677545</v>
       </c>
       <c r="M15" t="n">
-        <v>6.263804890398386</v>
+        <v>6.28797120603835</v>
       </c>
       <c r="N15" t="n">
-        <v>52.26533338571867</v>
+        <v>52.62875349763429</v>
       </c>
       <c r="O15" t="n">
-        <v>7.229476702066248</v>
+        <v>7.254567767802179</v>
       </c>
       <c r="P15" t="n">
-        <v>367.0087468089725</v>
+        <v>367.115652394019</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -32021,28 +32161,28 @@
         <v>0.0795</v>
       </c>
       <c r="I16" t="n">
-        <v>0.2636824173935685</v>
+        <v>0.2599054921180797</v>
       </c>
       <c r="J16" t="n">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="K16" t="n">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="L16" t="n">
-        <v>0.08171365940037612</v>
+        <v>0.08014428968682208</v>
       </c>
       <c r="M16" t="n">
-        <v>5.728282984488668</v>
+        <v>5.722261838829455</v>
       </c>
       <c r="N16" t="n">
-        <v>45.36708507490255</v>
+        <v>45.24353659933157</v>
       </c>
       <c r="O16" t="n">
-        <v>6.735509266187862</v>
+        <v>6.726331585591924</v>
       </c>
       <c r="P16" t="n">
-        <v>366.6275480968771</v>
+        <v>366.6678107156029</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -32099,28 +32239,28 @@
         <v>0.0578</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.08468665979332506</v>
+        <v>-0.07922227965235359</v>
       </c>
       <c r="J17" t="n">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="K17" t="n">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="L17" t="n">
-        <v>0.005697442044787615</v>
+        <v>0.005025224095590808</v>
       </c>
       <c r="M17" t="n">
-        <v>7.002241483643792</v>
+        <v>6.996109543087453</v>
       </c>
       <c r="N17" t="n">
-        <v>72.67143174489352</v>
+        <v>72.51532792421102</v>
       </c>
       <c r="O17" t="n">
-        <v>8.524754057736418</v>
+        <v>8.515593222096216</v>
       </c>
       <c r="P17" t="n">
-        <v>376.3844445304892</v>
+        <v>376.3261905995117</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -32158,7 +32298,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R432"/>
+  <dimension ref="A1:R434"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -71905,6 +72045,190 @@
         </is>
       </c>
     </row>
+    <row r="433">
+      <c r="A433" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-07 21:59:48+00:00</t>
+        </is>
+      </c>
+      <c r="B433" t="inlineStr">
+        <is>
+          <t>-37.74428271489333,176.4704789563871</t>
+        </is>
+      </c>
+      <c r="C433" t="inlineStr">
+        <is>
+          <t>-37.744942448754664,176.470814591011</t>
+        </is>
+      </c>
+      <c r="D433" t="inlineStr">
+        <is>
+          <t>-37.74557560898859,176.47120749063689</t>
+        </is>
+      </c>
+      <c r="E433" t="inlineStr">
+        <is>
+          <t>-37.746182713839474,176.4716189710595</t>
+        </is>
+      </c>
+      <c r="F433" t="inlineStr">
+        <is>
+          <t>-37.74677246839718,176.47208723005642</t>
+        </is>
+      </c>
+      <c r="G433" t="inlineStr">
+        <is>
+          <t>-37.74735031998691,176.47260477076088</t>
+        </is>
+      </c>
+      <c r="H433" t="inlineStr">
+        <is>
+          <t>-37.7478998240884,176.4731727036922</t>
+        </is>
+      </c>
+      <c r="I433" t="inlineStr">
+        <is>
+          <t>-37.748525892356554,176.47360735550154</t>
+        </is>
+      </c>
+      <c r="J433" t="inlineStr">
+        <is>
+          <t>-37.7491493892437,176.47404304368322</t>
+        </is>
+      </c>
+      <c r="K433" t="inlineStr">
+        <is>
+          <t>-37.749757154444076,176.47451264295665</t>
+        </is>
+      </c>
+      <c r="L433" t="inlineStr">
+        <is>
+          <t>-37.75032094412612,176.47506147689504</t>
+        </is>
+      </c>
+      <c r="M433" t="inlineStr">
+        <is>
+          <t>-37.75088903571493,176.47560347702648</t>
+        </is>
+      </c>
+      <c r="N433" t="inlineStr">
+        <is>
+          <t>-37.75146027992653,176.47613713834195</t>
+        </is>
+      </c>
+      <c r="O433" t="inlineStr">
+        <is>
+          <t>-37.75207369779247,176.47659095148774</t>
+        </is>
+      </c>
+      <c r="P433" t="inlineStr">
+        <is>
+          <t>-37.752633560552944,176.4771454239074</t>
+        </is>
+      </c>
+      <c r="Q433" t="inlineStr">
+        <is>
+          <t>-37.75316886847589,176.4777470568537</t>
+        </is>
+      </c>
+      <c r="R433" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-23 21:59:53+00:00</t>
+        </is>
+      </c>
+      <c r="B434" t="inlineStr">
+        <is>
+          <t>-37.74428475960388,176.47047340195843</t>
+        </is>
+      </c>
+      <c r="C434" t="inlineStr">
+        <is>
+          <t>-37.744943925498276,176.4708105794495</t>
+        </is>
+      </c>
+      <c r="D434" t="inlineStr">
+        <is>
+          <t>-37.745574255481536,176.47121094812368</t>
+        </is>
+      </c>
+      <c r="E434" t="inlineStr">
+        <is>
+          <t>-37.74618229496496,176.47161984453092</t>
+        </is>
+      </c>
+      <c r="F434" t="inlineStr">
+        <is>
+          <t>-37.74677226344312,176.47208760295686</t>
+        </is>
+      </c>
+      <c r="G434" t="inlineStr">
+        <is>
+          <t>-37.747350008848436,176.4726053268549</t>
+        </is>
+      </c>
+      <c r="H434" t="inlineStr">
+        <is>
+          <t>-37.74789673287,176.47317814364683</t>
+        </is>
+      </c>
+      <c r="I434" t="inlineStr">
+        <is>
+          <t>-37.748525575958446,176.47360790687688</t>
+        </is>
+      </c>
+      <c r="J434" t="inlineStr">
+        <is>
+          <t>-37.74914836148699,176.47404476574295</t>
+        </is>
+      </c>
+      <c r="K434" t="inlineStr">
+        <is>
+          <t>-37.74975539115247,176.47451551223105</t>
+        </is>
+      </c>
+      <c r="L434" t="inlineStr">
+        <is>
+          <t>-37.75031785162914,176.47506663439498</t>
+        </is>
+      </c>
+      <c r="M434" t="inlineStr">
+        <is>
+          <t>-37.75088844914474,176.47560448193795</t>
+        </is>
+      </c>
+      <c r="N434" t="inlineStr">
+        <is>
+          <t>-37.75146496603042,176.47612909302003</t>
+        </is>
+      </c>
+      <c r="O434" t="inlineStr">
+        <is>
+          <t>-37.75207564117226,176.47658782762358</t>
+        </is>
+      </c>
+      <c r="P434" t="inlineStr">
+        <is>
+          <t>-37.752631209812286,176.4771492977296</t>
+        </is>
+      </c>
+      <c r="Q434" t="inlineStr">
+        <is>
+          <t>-37.75316886847589,176.4777470568537</t>
+        </is>
+      </c>
+      <c r="R434" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
